--- a/artfynd/A 2979-2023 artfynd.xlsx
+++ b/artfynd/A 2979-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 2979-2023 artfynd.xlsx
+++ b/artfynd/A 2979-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12237,6 +12237,283 @@
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>121564852</v>
+      </c>
+      <c r="B79" t="n">
+        <v>90719</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="J79" t="inlineStr"/>
+      <c r="K79" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kvarnbrännan Nyvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>491993</v>
+      </c>
+      <c r="R79" t="n">
+        <v>7015319</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF79" t="inlineStr"/>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH79" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI79" t="inlineStr">
+        <is>
+          <t>Äldre luckig och flerskiktad grandominerad skog med inslag av tall, björk och sälg på frisk-fuktig, fuktig och frisk mark. Här finns träd av olika ålder och grovlek och träd med socklar förekommer. I skogsbeståndet finns stående, lutande och liggande död ved i måttlig mängd. Buskskikt med enstaka enbuskar och risdominerat fältskikt med inslag av örter. Flertalet myrstackar finns i skogsbeståndet. Äldre spår av skogsbruk i form av mossöverväxta stubbar.</t>
+        </is>
+      </c>
+      <c r="AJ79" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK79" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM79" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO79" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>121552949</v>
+      </c>
+      <c r="B80" t="n">
+        <v>57371</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kvarnbrännan Nyvik, Kvarnbrännan Nyvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>492135</v>
+      </c>
+      <c r="R80" t="n">
+        <v>7015106</v>
+      </c>
+      <c r="S80" t="n">
+        <v>7</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH80" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AJ80" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK80" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM80" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO80" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 2979-2023 artfynd.xlsx
+++ b/artfynd/A 2979-2023 artfynd.xlsx
@@ -12242,7 +12242,7 @@
         <v>121564852</v>
       </c>
       <c r="B79" t="n">
-        <v>90719</v>
+        <v>90720</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -12382,7 +12382,7 @@
         <v>121552949</v>
       </c>
       <c r="B80" t="n">
-        <v>57371</v>
+        <v>57372</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>

--- a/artfynd/A 2979-2023 artfynd.xlsx
+++ b/artfynd/A 2979-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY80"/>
+  <dimension ref="A1:AY82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12239,10 +12239,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>121564852</v>
+        <v>121552949</v>
       </c>
       <c r="B79" t="n">
-        <v>90720</v>
+        <v>57372</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -12255,44 +12255,47 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
-      <c r="J79" t="inlineStr"/>
-      <c r="K79" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N79" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Kvarnbrännan Nyvik, Jmt</t>
+          <t>Kvarnbrännan Nyvik, Kvarnbrännan Nyvik, Jmt</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>491993</v>
+        <v>492135</v>
       </c>
       <c r="R79" t="n">
-        <v>7015319</v>
+        <v>7015106</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -12330,7 +12333,6 @@
       <c r="AE79" t="b">
         <v>0</v>
       </c>
-      <c r="AF79" t="inlineStr"/>
       <c r="AG79" t="b">
         <v>0</v>
       </c>
@@ -12339,11 +12341,6 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AI79" t="inlineStr">
-        <is>
-          <t>Äldre luckig och flerskiktad grandominerad skog med inslag av tall, björk och sälg på frisk-fuktig, fuktig och frisk mark. Här finns träd av olika ålder och grovlek och träd med socklar förekommer. I skogsbeståndet finns stående, lutande och liggande död ved i måttlig mängd. Buskskikt med enstaka enbuskar och risdominerat fältskikt med inslag av örter. Flertalet myrstackar finns i skogsbeståndet. Äldre spår av skogsbruk i form av mossöverväxta stubbar.</t>
-        </is>
-      </c>
       <c r="AJ79" t="inlineStr">
         <is>
           <t>gran</t>
@@ -12356,12 +12353,12 @@
       </c>
       <c r="AM79" t="inlineStr">
         <is>
-          <t>Liggande död trädstam, utan markontakt</t>
+          <t>Trädstam på levande träd</t>
         </is>
       </c>
       <c r="AO79" t="inlineStr">
         <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
+          <t>Stem on living tree # Picea abies</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -12379,10 +12376,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121552949</v>
+        <v>121615588</v>
       </c>
       <c r="B80" t="n">
-        <v>57372</v>
+        <v>98105</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -12391,33 +12388,43 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
-      <c r="M80" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K80" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L80" t="inlineStr"/>
       <c r="N80" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -12425,17 +12432,17 @@
       </c>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Kvarnbrännan Nyvik, Kvarnbrännan Nyvik, Jmt</t>
+          <t>Kvarnbrännan Nyvik, Jmt</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492135</v>
+        <v>492017</v>
       </c>
       <c r="R80" t="n">
-        <v>7015106</v>
+        <v>7015219</v>
       </c>
       <c r="S80" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -12459,12 +12466,17 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-15</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2024-12-11</t>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Minst 5 st skott av knärot precis vid en hyggeskant för en nyligen kalavverkad yta. Vid besöket på denna fyndplats var marken snötäckt och stor del av bottenskiktet gick inte att se men det är mycket troligt att här finns betydligt fler knärotsskott. Mycket talar för det då denna fyndplats finns nära en annan fyndplats med över 1400 knärotsskott. Avverkningen på fyndplatsen är kopplad till ärendebeteckning A 2979-2023.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -12473,6 +12485,7 @@
       <c r="AE80" t="b">
         <v>0</v>
       </c>
+      <c r="AF80" t="inlineStr"/>
       <c r="AG80" t="b">
         <v>0</v>
       </c>
@@ -12481,24 +12494,9 @@
           <t>Granskog</t>
         </is>
       </c>
-      <c r="AJ80" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK80" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM80" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Picea abies</t>
+      <c r="AI80" t="inlineStr">
+        <is>
+          <t>Kanten av äldre granskog i direkt angränsning till kalhygge.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -12513,6 +12511,284 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>121615531</v>
+      </c>
+      <c r="B81" t="n">
+        <v>98105</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J81" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kvarnbrännan Nyvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>491989</v>
+      </c>
+      <c r="R81" t="n">
+        <v>7015240</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2024-12-15</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Minst 17 st skott av knärot på en nyligen kalavverkad öppen yta ca 11 meter från sammanhängande granskog vid hyggets kant. Vid besöket på denna fyndplats var marken snötäckt och till stora delar täckt av grenar efter avverkningen så mycket av fältskiktet gick inte att se. Så det är mycket troligt att här finns betydligt fler knärotsskott. Mycket talar för det då denna fyndplats angränsar till en annan fyndplats med över 1400 knärotsskott. Avverkningen på fyndplatsen är kopplad till ärendebeteckning A 2979-2023.</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH81" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI81" t="inlineStr">
+        <is>
+          <t>Kalavverkad tidigare äldre granskog med höga naturvärden. Enligt beslut från Skogsstyrelsen ska här återbeskogas med gran.</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>121564852</v>
+      </c>
+      <c r="B82" t="n">
+        <v>90720</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Kvarnbrännan Nyvik, Jmt</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>491993</v>
+      </c>
+      <c r="R82" t="n">
+        <v>7015319</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2024-12-11</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF82" t="inlineStr"/>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH82" t="inlineStr">
+        <is>
+          <t>Granskog</t>
+        </is>
+      </c>
+      <c r="AI82" t="inlineStr">
+        <is>
+          <t>Äldre luckig och flerskiktad grandominerad skog med inslag av tall, björk och sälg på frisk-fuktig, fuktig och frisk mark. Här finns träd av olika ålder och grovlek och träd med socklar förekommer. I skogsbeståndet finns stående, lutande och liggande död ved i måttlig mängd. Buskskikt med enstaka enbuskar och risdominerat fältskikt med inslag av örter. Flertalet myrstackar finns i skogsbeståndet. Äldre spår av skogsbruk i form av mossöverväxta stubbar.</t>
+        </is>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM82" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2979-2023 artfynd.xlsx
+++ b/artfynd/A 2979-2023 artfynd.xlsx
@@ -12376,7 +12376,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121615588</v>
+        <v>121615531</v>
       </c>
       <c r="B80" t="n">
         <v>98105</v>
@@ -12411,7 +12411,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -12436,10 +12436,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>492017</v>
+        <v>491989</v>
       </c>
       <c r="R80" t="n">
-        <v>7015219</v>
+        <v>7015240</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Minst 5 st skott av knärot precis vid en hyggeskant för en nyligen kalavverkad yta. Vid besöket på denna fyndplats var marken snötäckt och stor del av bottenskiktet gick inte att se men det är mycket troligt att här finns betydligt fler knärotsskott. Mycket talar för det då denna fyndplats finns nära en annan fyndplats med över 1400 knärotsskott. Avverkningen på fyndplatsen är kopplad till ärendebeteckning A 2979-2023.</t>
+          <t>Minst 17 st skott av knärot på en nyligen kalavverkad öppen yta ca 11 meter från sammanhängande granskog vid hyggets kant. Vid besöket på denna fyndplats var marken snötäckt och till stora delar täckt av grenar efter avverkningen så mycket av fältskiktet gick inte att se. Så det är mycket troligt att här finns betydligt fler knärotsskott. Mycket talar för det då denna fyndplats angränsar till en annan fyndplats med över 1400 knärotsskott. Avverkningen på fyndplatsen är kopplad till ärendebeteckning A 2979-2023.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Kanten av äldre granskog i direkt angränsning till kalhygge.</t>
+          <t>Kalavverkad tidigare äldre granskog med höga naturvärden. Enligt beslut från Skogsstyrelsen ska här återbeskogas med gran.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -12514,7 +12514,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121615531</v>
+        <v>121615588</v>
       </c>
       <c r="B81" t="n">
         <v>98105</v>
@@ -12549,7 +12549,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -12574,10 +12574,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>491989</v>
+        <v>492017</v>
       </c>
       <c r="R81" t="n">
-        <v>7015240</v>
+        <v>7015219</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Minst 17 st skott av knärot på en nyligen kalavverkad öppen yta ca 11 meter från sammanhängande granskog vid hyggets kant. Vid besöket på denna fyndplats var marken snötäckt och till stora delar täckt av grenar efter avverkningen så mycket av fältskiktet gick inte att se. Så det är mycket troligt att här finns betydligt fler knärotsskott. Mycket talar för det då denna fyndplats angränsar till en annan fyndplats med över 1400 knärotsskott. Avverkningen på fyndplatsen är kopplad till ärendebeteckning A 2979-2023.</t>
+          <t>Minst 5 st skott av knärot precis vid en hyggeskant för en nyligen kalavverkad yta. Vid besöket på denna fyndplats var marken snötäckt och stor del av bottenskiktet gick inte att se men det är mycket troligt att här finns betydligt fler knärotsskott. Mycket talar för det då denna fyndplats finns nära en annan fyndplats med över 1400 knärotsskott. Avverkningen på fyndplatsen är kopplad till ärendebeteckning A 2979-2023.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kalavverkad tidigare äldre granskog med höga naturvärden. Enligt beslut från Skogsstyrelsen ska här återbeskogas med gran.</t>
+          <t>Kanten av äldre granskog i direkt angränsning till kalhygge.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 2979-2023 artfynd.xlsx
+++ b/artfynd/A 2979-2023 artfynd.xlsx
@@ -12376,7 +12376,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>121615531</v>
+        <v>121615588</v>
       </c>
       <c r="B80" t="n">
         <v>98105</v>
@@ -12411,7 +12411,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>5</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -12436,10 +12436,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>491989</v>
+        <v>492017</v>
       </c>
       <c r="R80" t="n">
-        <v>7015240</v>
+        <v>7015219</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="AC80" t="inlineStr">
         <is>
-          <t>Minst 17 st skott av knärot på en nyligen kalavverkad öppen yta ca 11 meter från sammanhängande granskog vid hyggets kant. Vid besöket på denna fyndplats var marken snötäckt och till stora delar täckt av grenar efter avverkningen så mycket av fältskiktet gick inte att se. Så det är mycket troligt att här finns betydligt fler knärotsskott. Mycket talar för det då denna fyndplats angränsar till en annan fyndplats med över 1400 knärotsskott. Avverkningen på fyndplatsen är kopplad till ärendebeteckning A 2979-2023.</t>
+          <t>Minst 5 st skott av knärot precis vid en hyggeskant för en nyligen kalavverkad yta. Vid besöket på denna fyndplats var marken snötäckt och stor del av bottenskiktet gick inte att se men det är mycket troligt att här finns betydligt fler knärotsskott. Mycket talar för det då denna fyndplats finns nära en annan fyndplats med över 1400 knärotsskott. Avverkningen på fyndplatsen är kopplad till ärendebeteckning A 2979-2023.</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -12496,7 +12496,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Kalavverkad tidigare äldre granskog med höga naturvärden. Enligt beslut från Skogsstyrelsen ska här återbeskogas med gran.</t>
+          <t>Kanten av äldre granskog i direkt angränsning till kalhygge.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -12514,7 +12514,7 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>121615588</v>
+        <v>121615531</v>
       </c>
       <c r="B81" t="n">
         <v>98105</v>
@@ -12549,7 +12549,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -12574,10 +12574,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492017</v>
+        <v>491989</v>
       </c>
       <c r="R81" t="n">
-        <v>7015219</v>
+        <v>7015240</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -12614,7 +12614,7 @@
       </c>
       <c r="AC81" t="inlineStr">
         <is>
-          <t>Minst 5 st skott av knärot precis vid en hyggeskant för en nyligen kalavverkad yta. Vid besöket på denna fyndplats var marken snötäckt och stor del av bottenskiktet gick inte att se men det är mycket troligt att här finns betydligt fler knärotsskott. Mycket talar för det då denna fyndplats finns nära en annan fyndplats med över 1400 knärotsskott. Avverkningen på fyndplatsen är kopplad till ärendebeteckning A 2979-2023.</t>
+          <t>Minst 17 st skott av knärot på en nyligen kalavverkad öppen yta ca 11 meter från sammanhängande granskog vid hyggets kant. Vid besöket på denna fyndplats var marken snötäckt och till stora delar täckt av grenar efter avverkningen så mycket av fältskiktet gick inte att se. Så det är mycket troligt att här finns betydligt fler knärotsskott. Mycket talar för det då denna fyndplats angränsar till en annan fyndplats med över 1400 knärotsskott. Avverkningen på fyndplatsen är kopplad till ärendebeteckning A 2979-2023.</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -12634,7 +12634,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Kanten av äldre granskog i direkt angränsning till kalhygge.</t>
+          <t>Kalavverkad tidigare äldre granskog med höga naturvärden. Enligt beslut från Skogsstyrelsen ska här återbeskogas med gran.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>

--- a/artfynd/A 2979-2023 artfynd.xlsx
+++ b/artfynd/A 2979-2023 artfynd.xlsx
@@ -1150,12 +1150,7 @@
         <v>107104821</v>
       </c>
       <c r="B5" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57672</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1199,10 +1194,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>491926.0845590806</v>
+        <v>491926</v>
       </c>
       <c r="R5" t="n">
-        <v>7015257.1469428</v>
+        <v>7015257</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1232,24 +1227,14 @@
           <t>2023-03-02</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-03-02</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Relativt färska ringhack-spår av tretåig hackspett längs flera meter på en granstam. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2979-2023.</t>
+          <t>Relativt färska ringhack av tretåig hackspett längs flera meter på en granstam. Obs! Fyndplatsen finns inom en avverkningsanmäld yta med beteckning A 2979-2023. Under hösten 2024 avverkades trädet med ringhacken och en del skog runt fyndplatsen trots att beslut kopplat till vite från Skogsstyrelsen anvisade verksamhetsutövaren Rödins Trä att ringhackade träd skulle sparas.</t>
         </is>
       </c>
       <c r="AD5" t="b">

--- a/artfynd/A 2979-2023 artfynd.xlsx
+++ b/artfynd/A 2979-2023 artfynd.xlsx
@@ -1150,7 +1150,7 @@
         <v>107104821</v>
       </c>
       <c r="B5" t="n">
-        <v>57672</v>
+        <v>57673</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2979-2023 artfynd.xlsx
+++ b/artfynd/A 2979-2023 artfynd.xlsx
@@ -1150,7 +1150,7 @@
         <v>107104821</v>
       </c>
       <c r="B5" t="n">
-        <v>57673</v>
+        <v>57685</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2979-2023 artfynd.xlsx
+++ b/artfynd/A 2979-2023 artfynd.xlsx
@@ -1150,7 +1150,7 @@
         <v>107104821</v>
       </c>
       <c r="B5" t="n">
-        <v>57685</v>
+        <v>57689</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 2979-2023 artfynd.xlsx
+++ b/artfynd/A 2979-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY88"/>
+  <dimension ref="A1:AZ88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -786,6 +791,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111573403</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -921,6 +931,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121564852</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1057,6 +1072,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107110954</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1198,6 +1218,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112733</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1339,6 +1364,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112899</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1484,6 +1514,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107113008</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1625,6 +1660,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107113206</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1761,6 +1801,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107113713</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1897,6 +1942,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107113823</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2042,6 +2092,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107113912</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2182,6 +2237,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107114221</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2327,6 +2387,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107114308</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2463,6 +2528,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107114341</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2604,6 +2674,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107114372</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2744,6 +2819,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107114422</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2884,6 +2964,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107114454</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -3025,6 +3110,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107140849</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -3166,6 +3256,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107141571</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -3302,6 +3397,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107141807</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3438,6 +3538,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107141808</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3579,6 +3684,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107141810</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3724,6 +3834,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107141813</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3860,6 +3975,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107178264</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -4005,6 +4125,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107178679</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -4146,6 +4271,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107178884</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -4282,6 +4412,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107179276</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -4418,6 +4553,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107179281</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -4563,6 +4703,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107179322</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4704,6 +4849,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108078538</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4845,6 +4995,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108105817</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4986,6 +5141,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108105827</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -5127,6 +5287,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108105886</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -5272,6 +5437,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107110537</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -5417,6 +5587,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107111198</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -5562,6 +5737,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107139572</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -5707,6 +5887,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107179197</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -5813,6 +5998,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111573439</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -5958,6 +6148,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107111357</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -6103,6 +6298,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107139963</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -6248,6 +6448,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107141540</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -6393,6 +6598,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107141809</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -6499,6 +6709,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111573805</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -6634,6 +6849,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107112793</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -6766,6 +6986,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121552949</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -6910,6 +7135,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107104821</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -7054,6 +7284,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107141559</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -7198,6 +7433,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107179286</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -7322,6 +7562,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107104940</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -7446,6 +7691,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107113363</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -7570,6 +7820,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107141249</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -7690,6 +7945,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107141361</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -7826,6 +8086,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108078516</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -7962,6 +8227,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108078554</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -8090,6 +8360,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108078561</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -8219,6 +8494,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107103641</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -8352,6 +8632,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107138690</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -8485,6 +8770,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109382549</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -8618,6 +8908,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109382950</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -8747,6 +9042,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109383411</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -8880,6 +9180,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109384096</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -9013,6 +9318,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109384739</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -9146,6 +9456,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109384963</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -9279,6 +9594,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109385255</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -9412,6 +9732,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109385593</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -9545,6 +9870,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109783017</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -9678,6 +10008,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110108571</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -9811,6 +10146,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110109364</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -9944,6 +10284,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110109996</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -10077,6 +10422,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110110402</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -10210,6 +10560,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110111003</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -10343,6 +10698,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110117630</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -10449,6 +10809,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111573395</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -10582,6 +10947,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121615531</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -10715,6 +11085,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121615588</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -10840,6 +11215,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110133095</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -10957,6 +11337,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107114381</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -11078,6 +11463,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107179224</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -11195,6 +11585,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107179288</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -11315,6 +11710,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110110681</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -11440,6 +11840,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110131315</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -11561,6 +11966,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/108105907</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -11694,6 +12104,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109783395</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -11827,6 +12242,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110109666</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -11960,6 +12380,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110110281</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -12093,6 +12518,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110110736</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -12226,6 +12656,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110110927</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -12359,8 +12794,102 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110111070</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>